--- a/artfynd/A 55554-2024 artfynd.xlsx
+++ b/artfynd/A 55554-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121974056</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55554-2024 artfynd.xlsx
+++ b/artfynd/A 55554-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121974056</v>
       </c>
       <c r="B2" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55554-2024 artfynd.xlsx
+++ b/artfynd/A 55554-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121974056</v>
       </c>
       <c r="B2" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55554-2024 artfynd.xlsx
+++ b/artfynd/A 55554-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,6 +791,327 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126312590</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96598</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>53</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hyttöfjärden, Hyttöfjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>626546</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6706806</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126312503</v>
+      </c>
+      <c r="B4" t="n">
+        <v>95794</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>210</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bondmuren, Bondmuren, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>626574</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6706747</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126312265</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96598</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>53</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hyttöfjärden, Hyttöfjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>626556</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6706807</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55554-2024 artfynd.xlsx
+++ b/artfynd/A 55554-2024 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>126312590</v>
       </c>
       <c r="B3" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>126312503</v>
       </c>
       <c r="B4" t="n">
-        <v>95794</v>
+        <v>95798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>126312265</v>
       </c>
       <c r="B5" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55554-2024 artfynd.xlsx
+++ b/artfynd/A 55554-2024 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>126312590</v>
       </c>
       <c r="B3" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>126312503</v>
       </c>
       <c r="B4" t="n">
-        <v>95798</v>
+        <v>95801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>126312265</v>
       </c>
       <c r="B5" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55554-2024 artfynd.xlsx
+++ b/artfynd/A 55554-2024 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>126312590</v>
       </c>
       <c r="B3" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>126312503</v>
       </c>
       <c r="B4" t="n">
-        <v>95801</v>
+        <v>95810</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>126312265</v>
       </c>
       <c r="B5" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
